--- a/New_York_Knicks_2025-26_stats.xlsx
+++ b/New_York_Knicks_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,63 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,6 +1932,63 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1889,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,6 +2717,63 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2617,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3331,6 +3502,63 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3377,7 +3605,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.18181818181818</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="4">
@@ -3387,7 +3615,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.09090909090909</v>
+        <v>15.83333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3397,7 +3625,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.63636363636364</v>
+        <v>15.58333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3407,17 +3635,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.090909090909092</v>
+        <v>10.33333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.444444444444445</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3427,17 +3655,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.4</v>
+        <v>8.727272727272727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.636363636363637</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
@@ -3447,7 +3675,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.4</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3457,7 +3685,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7</v>
+        <v>2.727272727272727</v>
       </c>
     </row>
     <row r="12">
@@ -3487,7 +3715,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3553,7 +3781,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.909090909090909</v>
+        <v>4.916666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3563,7 +3791,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7</v>
+        <v>4.272727272727272</v>
       </c>
     </row>
     <row r="5">
@@ -3573,7 +3801,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.272727272727273</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3583,7 +3811,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.555555555555555</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -3593,7 +3821,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.363636363636364</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3603,7 +3831,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.454545454545455</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3623,7 +3851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3633,7 +3861,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="12">
@@ -3643,7 +3871,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="13">
@@ -3663,7 +3891,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="15">
@@ -3719,7 +3947,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.63636363636364</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3">
@@ -3729,7 +3957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.4</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -3739,7 +3967,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2</v>
+        <v>6.727272727272728</v>
       </c>
     </row>
     <row r="5">
@@ -3749,7 +3977,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.818181818181818</v>
+        <v>5.583333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3759,7 +3987,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.454545454545454</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -3775,21 +4003,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Guerschon Yabusele</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Guerschon Yabusele</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.444444444444445</v>
+        <v>2.454545454545455</v>
       </c>
     </row>
     <row r="10">
@@ -3799,7 +4027,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.428571428571428</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="11">
@@ -3829,7 +4057,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.454545454545455</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -3891,7 +4119,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -3901,11 +4129,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.818181818181818</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3915,37 +4143,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.454545454545455</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Miles McBride</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.083333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.727272727272727</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Miles McBride</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.636363636363636</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -3955,7 +4183,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.454545454545455</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3965,7 +4193,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="10">
@@ -3975,7 +4203,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="11">
@@ -4049,7 +4277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,6 +4538,27 @@
         <v>231</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>140</v>
+      </c>
+      <c r="D13" t="n">
+        <v>132</v>
+      </c>
+      <c r="E13" t="n">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
